--- a/Week_3/optimim_chart.xlsx
+++ b/Week_3/optimim_chart.xlsx
@@ -21,13 +21,13 @@
     <t>Phases</t>
   </si>
   <si>
-    <t>Thrust</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimum velocity</t>
+    <t xml:space="preserve">Thrust (N)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power (watt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimum velocity (m/s)</t>
   </si>
   <si>
     <t xml:space="preserve">T_W value</t>
